--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9AE01EE-127E-42BF-A519-B6F361F4AAE1}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1327B0-F3FC-4D21-9B87-6BC14052BF7A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>CA Prepration.</t>
+  </si>
+  <si>
+    <t>Today I went to the mall for shopping.</t>
   </si>
 </sst>
 </file>
@@ -2002,27 +2005,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B27" s="14">
+        <v>300</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>0</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>240</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1327B0-F3FC-4D21-9B87-6BC14052BF7A}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61C9857-17F7-49D9-AA54-1AE2042CAB4F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Today I went to the mall for shopping.</t>
+  </si>
+  <si>
+    <t>learning C++.</t>
   </si>
 </sst>
 </file>
@@ -2052,26 +2055,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>40</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>210</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61C9857-17F7-49D9-AA54-1AE2042CAB4F}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18832266-C94A-4067-86E3-5019850BEF95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>learning C++.</t>
+  </si>
+  <si>
+    <t>learning Python.</t>
   </si>
 </sst>
 </file>
@@ -2101,26 +2104,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>90</v>
+      </c>
+      <c r="E29" s="14">
+        <v>40</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>180</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18832266-C94A-4067-86E3-5019850BEF95}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61BCEA5B-1F83-411E-86C3-8E04F6CEEA34}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>learning Python.</t>
+  </si>
+  <si>
+    <t>Preparing for CA.</t>
   </si>
 </sst>
 </file>
@@ -2150,26 +2153,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>50</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>150</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61BCEA5B-1F83-411E-86C3-8E04F6CEEA34}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA3050E3-7C0E-49B8-BAE4-93F3995419DE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2199,26 +2199,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>40</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>150</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA3050E3-7C0E-49B8-BAE4-93F3995419DE}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEEFAB9-383E-4ABC-8315-DB4A424C37DB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2245,26 +2245,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B32" s="14">
+        <v>400</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>40</v>
+      </c>
+      <c r="E32" s="14">
+        <v>20</v>
+      </c>
+      <c r="F32" s="14">
+        <v>350</v>
+      </c>
+      <c r="G32" s="14">
+        <v>7</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEEFAB9-383E-4ABC-8315-DB4A424C37DB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Preparing for CA.</t>
+  </si>
+  <si>
+    <t>Preparing for Analytical CA.</t>
   </si>
 </sst>
 </file>
@@ -546,10 +549,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2291,26 +2290,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>40</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>120</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC2CDFF1-3A01-4E96-91FF-4A013B91A995}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2336,26 +2336,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>45</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>150</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
+        <v>120</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>615</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC2CDFF1-3A01-4E96-91FF-4A013B91A995}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6BDB55-94CD-471E-88ED-AF7A0D6468AA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Preparing for Analytical CA.</t>
+  </si>
+  <si>
+    <t>not a nice day due to fever.</t>
   </si>
 </sst>
 </file>
@@ -549,6 +552,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2382,26 +2389,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6BDB55-94CD-471E-88ED-AF7A0D6468AA}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE0A02AD-DBDA-48DE-B0D0-496D0AED923B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2435,26 +2435,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>45</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>150</v>
+      </c>
+      <c r="G36" s="14">
+        <v>3</v>
+      </c>
+      <c r="H36" s="14">
+        <v>220</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>515</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{B5876652-59D8-4F88-BF96-60FB9A89E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE0A02AD-DBDA-48DE-B0D0-496D0AED923B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4D3302-5D07-4DA1-8590-26A8E584CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -552,10 +552,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2481,26 +2477,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B37" s="14">
+        <v>360</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>350</v>
+      </c>
+      <c r="G37" s="14">
+        <v>7</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4D3302-5D07-4DA1-8590-26A8E584CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2523,26 +2523,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>60</v>
+      </c>
+      <c r="D38" s="14">
+        <v>50</v>
+      </c>
+      <c r="E38" s="14">
+        <v>40</v>
+      </c>
+      <c r="F38" s="14">
+        <v>200</v>
+      </c>
+      <c r="G38" s="14">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14">
+        <v>150</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0EE8EDC-EDDF-4A7F-8500-34D2320F5D0B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" calcMode="manual" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -552,6 +552,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2569,26 +2573,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>40</v>
+      </c>
+      <c r="E39" s="14">
+        <v>30</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>6</v>
+      </c>
+      <c r="H39" s="14">
+        <v>140</v>
+      </c>
+      <c r="I39" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J39" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>
@@ -10563,7 +10591,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J38 J40:J401">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0EE8EDC-EDDF-4A7F-8500-34D2320F5D0B}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45473B05-9907-4327-9FCC-702D5DFE74E3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>not a nice day due to fever.</t>
+  </si>
+  <si>
+    <t>Preparing for Mid-term.</t>
   </si>
 </sst>
 </file>
@@ -2598,7 +2601,7 @@
         <v>140</v>
       </c>
       <c r="I39" s="14">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
         <v>990</v>
       </c>
       <c r="J39" s="14">
@@ -2619,532 +2622,1108 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>60</v>
+      </c>
+      <c r="D40" s="14">
+        <v>30</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
+        <f>IF(SUM(B40:F40,H40)=0," ",SUM(B40:F40,H40))</f>
+        <v>630</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="1"/>
+        <v>810</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B41" s="14">
+        <v>300</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>40</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>200</v>
+      </c>
+      <c r="I41" s="15">
+        <f t="shared" ref="I41:I47" si="2">IF(SUM(B41:F41,H41)=0," ",SUM(B41:F41,H41))</f>
+        <v>600</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B42" s="14">
+        <v>480</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="2"/>
+        <v>540</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>60</v>
+      </c>
+      <c r="D43" s="14">
+        <v>0</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>180</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="1"/>
+        <v>780</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B44" s="14">
+        <v>360</v>
+      </c>
+      <c r="C44" s="14">
+        <v>60</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>90</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="2"/>
+        <v>510</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="1"/>
+        <v>930</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>60</v>
+      </c>
+      <c r="D45" s="14">
+        <v>40</v>
+      </c>
+      <c r="E45" s="14">
+        <v>30</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>90</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="2"/>
+        <v>640</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>60</v>
+      </c>
+      <c r="D46" s="14">
+        <v>40</v>
+      </c>
+      <c r="E46" s="14">
+        <v>45</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>90</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="2"/>
+        <v>715</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" si="1"/>
+        <v>725</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A47" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>60</v>
+      </c>
+      <c r="D47" s="14">
+        <v>60</v>
+      </c>
+      <c r="E47" s="14">
+        <v>20</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>60</v>
+      </c>
+      <c r="I47" s="15">
+        <f t="shared" si="2"/>
+        <v>620</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B48" s="14">
+        <v>360</v>
+      </c>
+      <c r="C48" s="14">
+        <v>60</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>220</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B49" s="14">
+        <v>300</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>150</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B50" s="14">
+        <v>450</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>40</v>
+      </c>
+      <c r="E50" s="14">
+        <v>20</v>
+      </c>
+      <c r="F50" s="14">
+        <v>150</v>
+      </c>
+      <c r="G50" s="14">
+        <v>3</v>
+      </c>
+      <c r="H50" s="14">
+        <v>180</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>60</v>
+      </c>
+      <c r="D51" s="14">
+        <v>60</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>350</v>
+      </c>
+      <c r="G51" s="14">
+        <v>7</v>
+      </c>
+      <c r="H51" s="14">
+        <v>210</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+        <v>250</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B52" s="14">
+        <v>360</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>200</v>
+      </c>
+      <c r="G52" s="14">
+        <v>4</v>
+      </c>
+      <c r="H52" s="14">
+        <v>150</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B53" s="14">
+        <v>420</v>
+      </c>
+      <c r="C53" s="14">
+        <v>60</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>150</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A54" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B54" s="14">
+        <v>360</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>150</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A55" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B55" s="14">
+        <v>420</v>
+      </c>
+      <c r="C55" s="14">
+        <v>60</v>
+      </c>
+      <c r="D55" s="14">
+        <v>40</v>
+      </c>
+      <c r="E55" s="14">
+        <v>40</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>60</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A56" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B56" s="14">
+        <v>420</v>
+      </c>
+      <c r="C56" s="14">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14">
+        <v>60</v>
+      </c>
+      <c r="E56" s="14">
+        <v>20</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>60</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A57" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>20</v>
+      </c>
+      <c r="E57" s="14">
+        <v>30</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>60</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A58" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>40</v>
+      </c>
+      <c r="E58" s="14">
+        <v>20</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>30</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A59" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B59" s="14">
+        <v>480</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14">
+        <v>45</v>
+      </c>
+      <c r="E59" s="14">
+        <v>30</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>150</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+        <v>675</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A60" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="14">
+        <v>480</v>
+      </c>
+      <c r="C60" s="14">
+        <v>60</v>
+      </c>
+      <c r="D60" s="14">
+        <v>120</v>
+      </c>
+      <c r="E60" s="14">
+        <v>30</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>180</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A61" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="14">
+        <v>360</v>
+      </c>
+      <c r="C61" s="14">
+        <v>60</v>
+      </c>
+      <c r="D61" s="14">
+        <v>60</v>
+      </c>
+      <c r="E61" s="14">
+        <v>30</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>45</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>555</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A62" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="14">
+        <v>360</v>
+      </c>
+      <c r="C62" s="14">
+        <v>60</v>
+      </c>
+      <c r="D62" s="14">
+        <v>60</v>
+      </c>
+      <c r="E62" s="14">
+        <v>30</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>45</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>555</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A63" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>0</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>45</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>525</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>915</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>
@@ -3288,11 +3867,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="3">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="4">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3310,11 +3889,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3332,11 +3911,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3354,11 +3933,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3376,11 +3955,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3398,11 +3977,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3420,11 +3999,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3442,11 +4021,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3464,11 +4043,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3486,11 +4065,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3508,11 +4087,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3530,11 +4109,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3552,11 +4131,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3574,11 +4153,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3596,11 +4175,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3618,11 +4197,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3640,11 +4219,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3662,11 +4241,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3684,11 +4263,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3706,11 +4285,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3728,11 +4307,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3750,11 +4329,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3772,11 +4351,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3794,11 +4373,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3816,11 +4395,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3838,11 +4417,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3860,11 +4439,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3882,11 +4461,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3904,11 +4483,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3926,11 +4505,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3948,11 +4527,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3970,11 +4549,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3992,11 +4571,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4014,11 +4593,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4036,11 +4615,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4058,11 +4637,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4080,11 +4659,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4102,11 +4681,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4124,11 +4703,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4146,11 +4725,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4168,11 +4747,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4190,11 +4769,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4212,11 +4791,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4234,11 +4813,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4256,11 +4835,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4278,11 +4857,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4300,11 +4879,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4322,11 +4901,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4344,11 +4923,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4366,11 +4945,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4388,11 +4967,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4410,11 +4989,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4432,11 +5011,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4454,11 +5033,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4476,11 +5055,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4498,11 +5077,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4520,11 +5099,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4542,11 +5121,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4564,11 +5143,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4586,11 +5165,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4608,11 +5187,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4630,11 +5209,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4652,11 +5231,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4674,11 +5253,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4696,11 +5275,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="5">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="6">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4718,11 +5297,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4740,11 +5319,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4762,11 +5341,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4784,11 +5363,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4806,11 +5385,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4828,11 +5407,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4850,11 +5429,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4872,11 +5451,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4894,11 +5473,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4916,11 +5495,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4938,11 +5517,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4960,11 +5539,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4982,11 +5561,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5004,11 +5583,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5026,11 +5605,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5048,11 +5627,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5070,11 +5649,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5092,11 +5671,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5114,11 +5693,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5136,11 +5715,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5158,11 +5737,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5180,11 +5759,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5202,11 +5781,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5224,11 +5803,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5246,11 +5825,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5268,11 +5847,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5290,11 +5869,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5312,11 +5891,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5334,11 +5913,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5356,11 +5935,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5378,11 +5957,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5400,11 +5979,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5422,11 +6001,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5444,11 +6023,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5466,11 +6045,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5488,11 +6067,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5510,11 +6089,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5532,11 +6111,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5554,11 +6133,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5576,11 +6155,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5598,11 +6177,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5620,11 +6199,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5642,11 +6221,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5664,11 +6243,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5686,11 +6265,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5708,11 +6287,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5730,11 +6309,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5752,11 +6331,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5774,11 +6353,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5796,11 +6375,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5818,11 +6397,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5840,11 +6419,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5862,11 +6441,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5884,11 +6463,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5906,11 +6485,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5928,11 +6507,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5950,11 +6529,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5972,11 +6551,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5994,11 +6573,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6016,11 +6595,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6038,11 +6617,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6060,11 +6639,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6082,11 +6661,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6104,11 +6683,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="7">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="8">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6126,11 +6705,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6148,11 +6727,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6170,11 +6749,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6192,11 +6771,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6214,11 +6793,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6236,11 +6815,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6258,11 +6837,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6280,11 +6859,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6302,11 +6881,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6324,11 +6903,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6346,11 +6925,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6368,11 +6947,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6390,11 +6969,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6412,11 +6991,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6434,11 +7013,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6456,11 +7035,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6478,11 +7057,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6500,11 +7079,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6522,11 +7101,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6544,11 +7123,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6566,11 +7145,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6588,11 +7167,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6610,11 +7189,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6632,11 +7211,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6654,11 +7233,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6676,11 +7255,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6698,11 +7277,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6720,11 +7299,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6742,11 +7321,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6764,11 +7343,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6786,11 +7365,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6808,11 +7387,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6830,11 +7409,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6852,11 +7431,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6874,11 +7453,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6896,11 +7475,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6918,11 +7497,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6940,11 +7519,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6962,11 +7541,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6984,11 +7563,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7006,11 +7585,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7028,11 +7607,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7050,11 +7629,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7072,11 +7651,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7094,11 +7673,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7116,11 +7695,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7138,11 +7717,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7160,11 +7739,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7182,11 +7761,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7204,11 +7783,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7226,11 +7805,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7248,11 +7827,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7270,11 +7849,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7292,11 +7871,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7314,11 +7893,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7336,11 +7915,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7358,11 +7937,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7380,11 +7959,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7402,11 +7981,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7424,11 +8003,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7446,11 +8025,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7468,11 +8047,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7490,11 +8069,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7512,11 +8091,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="9">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="10">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7534,11 +8113,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7556,11 +8135,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7578,11 +8157,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7600,11 +8179,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7622,11 +8201,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7644,11 +8223,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7666,11 +8245,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7688,11 +8267,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7710,11 +8289,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7732,11 +8311,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7754,11 +8333,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7776,11 +8355,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7798,11 +8377,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7820,11 +8399,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7842,11 +8421,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7864,11 +8443,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7886,11 +8465,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7908,11 +8487,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7930,11 +8509,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7952,11 +8531,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7974,11 +8553,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7996,11 +8575,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8018,11 +8597,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8040,11 +8619,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8062,11 +8641,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8084,11 +8663,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8106,11 +8685,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8128,11 +8707,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8150,11 +8729,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8172,11 +8751,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8194,11 +8773,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8216,11 +8795,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8238,11 +8817,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8260,11 +8839,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8282,11 +8861,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8304,11 +8883,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8326,11 +8905,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8348,11 +8927,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8370,11 +8949,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8392,11 +8971,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8414,11 +8993,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8436,11 +9015,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8458,11 +9037,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8480,11 +9059,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8502,11 +9081,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8524,11 +9103,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8546,11 +9125,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8568,11 +9147,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8590,11 +9169,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8612,11 +9191,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8634,11 +9213,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8656,11 +9235,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8678,11 +9257,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8700,11 +9279,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8722,11 +9301,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8744,11 +9323,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8766,11 +9345,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8788,11 +9367,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8810,11 +9389,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8832,11 +9411,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8854,11 +9433,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8876,11 +9455,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8898,11 +9477,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8920,11 +9499,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="11">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="12">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8942,11 +9521,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8964,11 +9543,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8986,11 +9565,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9008,11 +9587,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9030,11 +9609,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9052,11 +9631,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9074,11 +9653,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9096,11 +9675,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9118,11 +9697,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9140,11 +9719,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9162,11 +9741,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9184,11 +9763,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9206,11 +9785,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9228,11 +9807,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9250,11 +9829,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9272,11 +9851,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9294,11 +9873,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9316,11 +9895,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9338,11 +9917,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9360,11 +9939,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9382,11 +9961,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9404,11 +9983,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9426,11 +10005,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9448,11 +10027,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9470,11 +10049,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9492,11 +10071,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9514,11 +10093,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9536,11 +10115,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9558,11 +10137,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9580,11 +10159,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9602,11 +10181,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9624,11 +10203,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9646,11 +10225,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9668,11 +10247,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9690,11 +10269,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9712,11 +10291,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9734,11 +10313,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9756,11 +10335,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9778,11 +10357,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9800,11 +10379,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9822,11 +10401,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9844,11 +10423,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9866,11 +10445,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9888,11 +10467,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9910,11 +10489,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9932,11 +10511,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9954,11 +10533,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9976,11 +10555,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9998,11 +10577,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10020,11 +10599,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10042,11 +10621,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10064,11 +10643,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10086,11 +10665,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10108,11 +10687,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10130,11 +10709,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10152,11 +10731,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10174,11 +10753,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10196,11 +10775,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10218,11 +10797,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10240,11 +10819,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10262,11 +10841,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10284,11 +10863,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10306,11 +10885,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10328,11 +10907,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="13">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="14">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10350,11 +10929,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10372,11 +10951,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10394,11 +10973,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10416,11 +10995,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10438,11 +11017,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10460,11 +11039,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10482,11 +11061,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10504,11 +11083,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10526,11 +11105,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10548,11 +11127,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10570,11 +11149,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45473B05-9907-4327-9FCC-702D5DFE74E3}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233A6E57-DE3B-4073-91B2-8ED246042F26}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3726,26 +3726,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="14">
+        <v>420</v>
+      </c>
+      <c r="C64" s="14">
+        <v>60</v>
+      </c>
+      <c r="D64" s="14">
+        <v>40</v>
+      </c>
+      <c r="E64" s="14">
+        <v>30</v>
+      </c>
+      <c r="F64" s="14">
+        <v>150</v>
+      </c>
+      <c r="G64" s="14">
+        <v>3</v>
+      </c>
+      <c r="H64" s="14">
+        <v>180</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233A6E57-DE3B-4073-91B2-8ED246042F26}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51452B2A-62FF-40D9-99FC-78B5EAA28706}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3772,26 +3772,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="14">
+        <v>420</v>
+      </c>
+      <c r="C65" s="14">
+        <v>45</v>
+      </c>
+      <c r="D65" s="14">
+        <v>20</v>
+      </c>
+      <c r="E65" s="14">
+        <v>30</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>180</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>695</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>745</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51452B2A-62FF-40D9-99FC-78B5EAA28706}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB072EAB-9FE0-41E5-B7B4-CD6B03DE3418}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3818,26 +3818,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="14">
+        <v>420</v>
+      </c>
+      <c r="C66" s="14">
+        <v>45</v>
+      </c>
+      <c r="D66" s="14">
+        <v>60</v>
+      </c>
+      <c r="E66" s="14">
+        <v>30</v>
+      </c>
+      <c r="F66" s="14">
+        <v>200</v>
+      </c>
+      <c r="G66" s="14">
+        <v>4</v>
+      </c>
+      <c r="H66" s="14">
+        <v>150</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB072EAB-9FE0-41E5-B7B4-CD6B03DE3418}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{976E4E83-C1DF-4972-9255-31B460344EB0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="2810" windowWidth="14400" windowHeight="7270" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3864,26 +3864,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>30</v>
+      </c>
+      <c r="D67" s="14">
+        <v>40</v>
+      </c>
+      <c r="E67" s="14">
+        <v>30</v>
+      </c>
+      <c r="F67" s="14">
+        <v>350</v>
+      </c>
+      <c r="G67" s="14">
+        <v>7</v>
+      </c>
+      <c r="H67" s="14">
+        <v>120</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{976E4E83-C1DF-4972-9255-31B460344EB0}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{969C824D-A5DA-4967-9FA3-82204833FC63}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="2810" windowWidth="14400" windowHeight="7270" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3910,26 +3910,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="14">
+        <v>420</v>
+      </c>
+      <c r="C68" s="14">
+        <v>40</v>
+      </c>
+      <c r="D68" s="14">
+        <v>60</v>
+      </c>
+      <c r="E68" s="14">
+        <v>60</v>
+      </c>
+      <c r="F68" s="14">
+        <v>300</v>
+      </c>
+      <c r="G68" s="14">
+        <v>6</v>
+      </c>
+      <c r="H68" s="14">
+        <v>180</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{7FA6F777-5D3A-4E83-8911-7E1007D4458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{969C824D-A5DA-4967-9FA3-82204833FC63}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -555,10 +555,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3956,26 +3952,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="14">
+        <v>420</v>
+      </c>
+      <c r="C69" s="14">
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <v>60</v>
+      </c>
+      <c r="E69" s="14">
+        <v>30</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>180</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5DB294-3C58-4D6B-B18A-275333F276F7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3998,26 +3998,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="14">
+        <v>420</v>
+      </c>
+      <c r="C70" s="14">
+        <v>30</v>
+      </c>
+      <c r="D70" s="14">
+        <v>0</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>210</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="3">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="4">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5DB294-3C58-4D6B-B18A-275333F276F7}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A1F915-5EB6-45D0-934A-063E596A22F5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Preparing for Mid-term.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning python. </t>
   </si>
 </sst>
 </file>
@@ -555,6 +558,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4044,26 +4051,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="14">
+        <v>360</v>
+      </c>
+      <c r="C71" s="14">
+        <v>0</v>
+      </c>
+      <c r="D71" s="14">
+        <v>40</v>
+      </c>
+      <c r="E71" s="14">
+        <v>45</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>120</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>565</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>875</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A1F915-5EB6-45D0-934A-063E596A22F5}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{993BA97F-71F6-4448-BA7C-A5FF75FB0090}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t xml:space="preserve">learning python. </t>
+  </si>
+  <si>
+    <t>learning python.</t>
   </si>
 </sst>
 </file>
@@ -4097,26 +4100,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>30</v>
+      </c>
+      <c r="D72" s="14">
+        <v>60</v>
+      </c>
+      <c r="E72" s="14">
+        <v>30</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>180</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{993BA97F-71F6-4448-BA7C-A5FF75FB0090}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{99CA4041-9A84-4766-91B1-84BDC9E20305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A64D0320-0574-40B9-B3C3-B8953160E667}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4146,48 +4146,96 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="14">
+        <v>420</v>
+      </c>
+      <c r="C73" s="14">
+        <v>60</v>
+      </c>
+      <c r="D73" s="14">
+        <v>60</v>
+      </c>
+      <c r="E73" s="14">
+        <v>30</v>
+      </c>
+      <c r="F73" s="14">
+        <v>200</v>
+      </c>
+      <c r="G73" s="14">
+        <v>4</v>
+      </c>
+      <c r="H73" s="14">
+        <v>180</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="14">
+        <v>420</v>
+      </c>
+      <c r="C74" s="14">
+        <v>60</v>
+      </c>
+      <c r="D74" s="14">
+        <v>60</v>
+      </c>
+      <c r="E74" s="14">
+        <v>30</v>
+      </c>
+      <c r="F74" s="14">
+        <v>300</v>
+      </c>
+      <c r="G74" s="14">
+        <v>6</v>
+      </c>
+      <c r="H74" s="14">
+        <v>180</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>
